--- a/孤云支线18Boss数值表_v2.xlsx
+++ b/孤云支线18Boss数值表_v2.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="孤云支线18Boss" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特性代码对照" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="九维说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="孤云支线18Boss" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="特性代码对照" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="九维说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,7 +643,11 @@
       <c r="N3" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Boss特性代码（v6新版）</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -853,7 +857,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>miniArmor</t>
+          <t>armorShield</t>
         </is>
       </c>
     </row>
@@ -908,7 +912,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>lowHpBerserk</t>
+          <t>armorBreak,hamstringStrike,armorShield,lowHpBerserk</t>
         </is>
       </c>
     </row>
@@ -920,7 +924,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>沈千山帐前哨长·杜威</t>
+          <t>帐前哨长·杜威</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -959,9 +963,13 @@
         <v>3</v>
       </c>
       <c r="N9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>veinBreak</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1014,7 +1022,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>miniFrost</t>
+          <t>chillAura</t>
         </is>
       </c>
     </row>
@@ -1065,9 +1073,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>veinBreak,armorShield</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1120,7 +1132,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>miniBleed</t>
+          <t>bloodBlade,venomInfuse</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1187,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>highDodge</t>
+          <t>bloodBlade,veinBreak,shadowStep</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1242,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>berserkSummon</t>
+          <t>celestialShield,lowHpBerserk,bloodBlade,chillAura</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1297,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>lowHpBerserk</t>
+          <t>hamstringStrike,lowHpBerserk</t>
         </is>
       </c>
     </row>
@@ -1336,9 +1348,13 @@
         <v>5</v>
       </c>
       <c r="N16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>celestialCleanse,lowHpBerserk</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1391,7 +1407,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>armorBreak</t>
+          <t>celestialShield,armorBreak</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1462,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>armorBreak</t>
+          <t>celestialShield,bloodBlade</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1517,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>pointStrike</t>
+          <t>celestialCleanse,veinBreak,hamstringStrike</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1572,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>shieldPurityBerserk</t>
+          <t>veinBreak,hamstringStrike,celestialShield,celestialCleanse,celestialBurn</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1614,148 +1630,199 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>M6·M30·M32</t>
+          <t>M6·M12·M30</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>玩家DEF仅剩55%；每次命中玩家DEF-2（紫霄清心诀-1）</t>
+          <t>玩家DEF仅剩55%，每次命中DEF-5%（紫霄清心诀时DEF-2%）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>miniArmor</t>
+          <t>hamstringStrike</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M4·M8·M12·M26·M34·M36</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>开场护体盾 = 20% HP</t>
+          <t>每回合断筋+rank，上限15层（每层攻击-2%减速2%），25层引爆筋断力竭（攻击归零2回合）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>lowHpBerserk</t>
+          <t>veinBreak</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>M12·M26</t>
+          <t>M14·M18·M22·M34·M36</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>≤30% HP：ATK×1.3，SPEED+0.08</t>
+          <t>每回合断脉+rank，上限15层（每层减内力2%减速2%），25层引爆脉路全封（扣除25%最大内力）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>miniFrost</t>
+          <t>chillAura</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>M16</t>
+          <t>M16·M24</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>每回合玩家寒气+1（每层寒气减速、增耗内）</t>
+          <t>每回合寒气+rank，上限15层（每层减速4%），25层引爆极度寒冷（冰冻1回合）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>miniBleed</t>
+          <t>bloodBlade</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>M20</t>
+          <t>M20·M22·M24·M32</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>每回合玩家流血+2（上限10；流血每回合扣HP=层数）</t>
+          <t>每回合流血+rank，上限15层（每层15伤害），25层引爆血崩（扣除15%当前血量）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>highDodge</t>
+          <t>venomInfuse</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>M22</t>
+          <t>M20</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>基础DODGE=30（极高）；≤50%HP：DODGE+5→35</t>
+          <t>每回合中毒+rank，上限15层（每层8伤害+4内力），25层引爆毒爆（扣除7.5%血+7.5%内）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>berserkSummon</t>
+          <t>lowHpBerserk</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>M12·M24·M26·M28</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>≤70%HP：ATK×1.15,SPEED+0.05；≤30%HP：ATK×1.2,DEF×1.15</t>
+          <t>≤30%HP触发：ATK×1.5，SPEED+rank×0.3，持续5回合</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>pointStrike</t>
+          <t>shadowStep</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>M34</t>
+          <t>M22</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>命中30%打穴：额外伤害=ATK×30%, 玩家SPEED-0.25(≥0.5)</t>
+          <t>基础闪避75%；≤50%HP闪避×1.5；闪避回血10%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>shieldPurityBerserk</t>
+          <t>armorShield</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
+          <t>M10·M12·M18</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>护体真气：开场20%最大HP护体盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>celestialShield</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M24·M30·M32·M36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天罡护体：开场30%最大HP护体盾</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>celestialCleanse</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M28·M34·M36</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>天罡净化：≤50%HP净化所有负面+回血30%（每场一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>celestialBurn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>M36</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>开场护体25%HP；≤50%HP净化+回血20%；≤15%HP ATK×2,DEF=0</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>天罡燃命：≤10%HP触发ATK×2,SPEED×2,DEF×0.5（每场一次）</t>
         </is>
       </c>
     </row>
